--- a/VO_Manifest.xlsx
+++ b/VO_Manifest.xlsx
@@ -448,12 +448,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vo_review_landing</t>
+          <t>vo_review_landing_v2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>नमस्ते दोस्त, मैं हूँ स्विफ़्टी। आज हम एक कहानी पढ़ेंगे—कालू-मालू-आलू।</t>
+          <t>नमस्ते दोस्त, मैं हूँ स्विफ़्टी। आज हम एक कहानी पढ़ेंगे—आलू-मालू-कालू।</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>sfx_puppy_bark</t>
+          <t>sfx_dog_bark</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SFX (असली रिकॉर्डिंग, AI नहीं): छोटे पिल्ले की 3 प्यारी, पतली भौंक — भौं, भौं, भौं (~0.8 सेकंड)। कहानी पेज 8 पर VO “…उसे सुनाई दिया,” के तुरंत बाद बजती है। स्रोत: freesound.org/s/591137 (dtmendes, cockapoo puppy), लाइसेंस CC0; पिच थोड़ी ऊँची की गई।</t>
+          <t>SFX (असली रिकॉर्डिंग, AI नहीं): बड़े कुत्ते (St. Bernard) की 3 भारी भौंक — भौं, भौं, भौं (~1.3 सेकंड)। कहानी पेज 8 पर VO “…उसे सुनाई दिया,” के तुरंत बाद बजती है। स्रोत: freesound.org/s/784914 (Primitv094), लाइसेंस CC0।</t>
         </is>
       </c>
     </row>

--- a/VO_Manifest.xlsx
+++ b/VO_Manifest.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -748,538 +748,550 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>vo_dadi_hint3</t>
+          <t>vo_dadi_hint1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>मालू से आलू लाने के लिए दादी ने कहा था। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>फिर से कोशिश कीजिए, कहानी याद कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>vo_q_kaalu</t>
+          <t>vo_dadi_hint3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>कालू कौन है?</t>
+          <t>मालू से आलू लाने के लिए दादी ने कहा था। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>vo_o_opt_kutta</t>
+          <t>vo_q_kaalu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>कुत्ता</t>
+          <t>कालू कौन है?</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>vo_o_opt_gaay</t>
+          <t>vo_o_opt_kutta</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>गाय</t>
+          <t>कुत्ता</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>vo_o_opt_billi</t>
+          <t>vo_o_opt_gaay</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>बिल्ली</t>
+          <t>गाय</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>vo_kaalu_hint3</t>
+          <t>vo_o_opt_billi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>कालू एक कुत्ता है। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>बिल्ली</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>vo_q_vegetable</t>
+          <t>vo_kaalu_hint3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>मालू ने बगीचे से कौन-सी सब्ज़ी तोड़ी?</t>
+          <t>कालू एक कुत्ता है। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>vo_o_opt_baingan</t>
+          <t>vo_q_vegetable</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>बैंगन</t>
+          <t>मालू ने बगीचे से कौन-सी सब्ज़ी तोड़ी?</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>vo_o_opt_aloo</t>
+          <t>vo_o_opt_baingan</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>आलू</t>
+          <t>बैंगन</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>vo_o_opt_gajar</t>
+          <t>vo_o_opt_aloo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>गाजर</t>
+          <t>आलू</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>vo_review_vegetable_hint3_v2</t>
+          <t>vo_o_opt_gajar</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>मालू ने बगीचे से बैंगन तोड़े। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>गाजर</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>vo_review_pt3</t>
+          <t>vo_review_vegetable_hint3_v2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>वाह! अब आपकी बारी।</t>
+          <t>मालू ने बगीचे से बैंगन तोड़े। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>vo_review_puzzle_cards</t>
+          <t>vo_review_pt3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>प्रश्नचिह्न पर टैप करके प्रश्नों के उत्तर दीजिए। फिर चित्र के टुकड़ों को खिसकाकर चित्र पूरा कीजिए।</t>
+          <t>वाह! अब आपकी बारी।</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>vo_q_soil</t>
+          <t>vo_review_puzzle_cards</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>आलू कहाँ उगते हैं?</t>
+          <t>प्रश्नचिह्न पर टैप करके प्रश्नों के उत्तर दीजिए। फिर चित्र के टुकड़ों को खिसकाकर चित्र पूरा कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>vo_o_opt_ped</t>
+          <t>vo_q_soil</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>पेड़ पर</t>
+          <t>आलू कहाँ उगते हैं?</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>vo_o_opt_mitti</t>
+          <t>vo_o_opt_ped</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>मिट्टी के अंदर</t>
+          <t>पेड़ पर</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>vo_review_water_option</t>
+          <t>vo_o_opt_mitti</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>पानी के अंदर।</t>
+          <t>मिट्टी के अंदर</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>vo_review_soil_hint3</t>
+          <t>vo_review_water_option</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>आलू मिट्टी के अंदर उगते हैं। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>पानी के अंदर।</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>vo_q_sad</t>
+          <t>vo_review_soil_hint3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>आलू न मिलने पर मालू कैसा महसूस कर रहा था?</t>
+          <t>आलू मिट्टी के अंदर उगते हैं। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>vo_o_face_udaas</t>
+          <t>vo_q_sad</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>उदास</t>
+          <t>आलू न मिलने पर मालू कैसा महसूस कर रहा था?</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>vo_o_face_dara</t>
+          <t>vo_o_face_udaas</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>डरा हुआ</t>
+          <t>उदास</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>vo_o_face_khush</t>
+          <t>vo_o_face_dara</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>खुश</t>
+          <t>डरा हुआ</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>vo_review_sad_hint3</t>
+          <t>vo_o_face_khush</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>मालू उदास हो गया था। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>खुश</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>vo_q_basket</t>
+          <t>vo_review_sad_hint3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>मालू ने दादी के आगे खाली टोकरी क्यों रख दी थी?</t>
+          <t>मालू उदास हो गया था। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>vo_o_t_bhookh</t>
+          <t>vo_q_basket</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>उसे भूख लगी थी</t>
+          <t>मालू ने दादी के आगे खाली टोकरी क्यों रख दी थी?</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>vo_o_t_nahi_mile_v2</t>
+          <t>vo_o_t_bhookh</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>उसे आलू नहीं मिले थे</t>
+          <t>उसे भूख लगी थी</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>vo_o_t_tooti</t>
+          <t>vo_o_t_nahi_mile_v2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>टोकरी टूट गई थी</t>
+          <t>उसे आलू नहीं मिले थे</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>vo_review_basket_hint3</t>
+          <t>vo_o_t_tooti</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>उसे आलू नहीं मिले थे। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>टोकरी टूट गई थी</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>vo_fill_prompt</t>
+          <t>vo_review_basket_hint3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>सही शब्द चुनकर वाक्य पूरा कीजिए।</t>
+          <t>उसे आलू नहीं मिले थे। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>vo_o_maalu</t>
+          <t>vo_fill_prompt</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>मालू</t>
+          <t>सही शब्द चुनकर वाक्य पूरा कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>vo_o_kaalu</t>
+          <t>vo_o_maalu</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>कालू</t>
+          <t>मालू</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>vo_fill_answer</t>
+          <t>vo_o_kaalu</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>कालू ने आलू ढूँढ़ने में मालू की मदद की।</t>
+          <t>कालू</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>vo_q_p4</t>
+          <t>vo_fill_answer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>दादी ने ‘ध्यान से देखो’ क्यों कहा?</t>
+          <t>कालू ने आलू ढूँढ़ने में मालू की मदद की।</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>vo_o_t_chhipe</t>
+          <t>vo_q_p4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>आलू मिट्टी में छिपे थे</t>
+          <t>दादी ने ‘ध्यान से देखो’ क्यों कहा?</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>vo_o_t_so_raha</t>
+          <t>vo_o_t_chhipe</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>मालू सो रहा था</t>
+          <t>आलू मिट्टी में छिपे थे</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>vo_o_t_andhera</t>
+          <t>vo_o_t_so_raha</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>बगीचे में अँधेरा था</t>
+          <t>मालू सो रहा था</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>vo_p4_hint3</t>
+          <t>vo_o_t_andhera</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>आलू मिट्टी में छिपे थे। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>बगीचे में अँधेरा था</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>vo_q_khoj</t>
+          <t>vo_p4_hint3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>आलू मिलने पर मालू ने कालू से क्या कहा?</t>
+          <t>आलू मिट्टी में छिपे थे। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>vo_khoj_ghar</t>
+          <t>vo_q_khoj</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>घर चलो, कालू।</t>
+          <t>आलू मिलने पर मालू ने कालू से क्या कहा?</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>vo_khoj_wah</t>
+          <t>vo_khoj_ghar</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>वाह कालू! ढूँढ़ निकाले आलू।</t>
+          <t>घर चलो, कालू।</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>vo_khoj_khaen</t>
+          <t>vo_khoj_wah</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>कालू, आओ खाएँ आलू।</t>
+          <t>वाह कालू! ढूँढ़ निकाले आलू।</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>vo_khoj_hint3</t>
+          <t>vo_khoj_khaen</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>मालू ने कहा, वाह कालू! ढूँढ़ निकाले आलू। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>कालू, आओ खाएँ आलू।</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>vo_review_puzzle_assemble</t>
+          <t>vo_khoj_hint3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>अब चित्र के टुकड़ों को खिसकाकर चित्र पूरा कीजिए।</t>
+          <t>मालू ने कहा, वाह कालू! ढूँढ़ निकाले आलू। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>vo_review_celebrate_v2</t>
+          <t>vo_review_puzzle_assemble</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>बहुत बढ़िया, दोस्त! तुमने कमाल कर दिया!</t>
+          <t>अब चित्र के टुकड़ों को खिसकाकर चित्र पूरा कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>vo_review_celebrate_v2</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>बहुत बढ़िया, दोस्त! तुमने कमाल कर दिया!</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>sfx_dog_bark</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>SFX (असली रिकॉर्डिंग, AI नहीं): बड़े कुत्ते (St. Bernard) की 3 भारी भौंक — भौं, भौं, भौं (~1.3 सेकंड)। कहानी पेज 8 पर VO “…उसे सुनाई दिया,” के तुरंत बाद बजती है। स्रोत: freesound.org/s/784914 (Primitv094), लाइसेंस CC0।</t>
         </is>

--- a/VO_Manifest.xlsx
+++ b/VO_Manifest.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -820,478 +820,502 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>vo_kaalu_hint3</t>
+          <t>vo_kaalu_hint1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>कालू एक कुत्ता है। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>फिर से कोशिश कीजिए, चित्र देखकर पहचानिए।</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>vo_q_vegetable</t>
+          <t>vo_kaalu_hint3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>मालू ने बगीचे से कौन-सी सब्ज़ी तोड़ी?</t>
+          <t>कालू एक कुत्ता है। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>vo_o_opt_baingan</t>
+          <t>vo_q_vegetable</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>बैंगन</t>
+          <t>मालू ने बगीचे से कौन-सी सब्ज़ी तोड़ी?</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>vo_o_opt_aloo</t>
+          <t>vo_o_opt_baingan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>आलू</t>
+          <t>बैंगन</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>vo_o_opt_gajar</t>
+          <t>vo_o_opt_aloo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>गाजर</t>
+          <t>आलू</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>vo_review_vegetable_hint3_v2</t>
+          <t>vo_o_opt_gajar</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>मालू ने बगीचे से बैंगन तोड़े। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>गाजर</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>vo_review_pt3</t>
+          <t>vo_review_vegetable_hint1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>वाह! अब आपकी बारी।</t>
+          <t>फिर से कोशिश कीजिए, कहानी याद कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>vo_review_puzzle_cards</t>
+          <t>vo_review_vegetable_hint3_v2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>प्रश्नचिह्न पर टैप करके प्रश्नों के उत्तर दीजिए। फिर चित्र के टुकड़ों को खिसकाकर चित्र पूरा कीजिए।</t>
+          <t>मालू ने बगीचे से बैंगन तोड़े। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>vo_q_soil</t>
+          <t>vo_review_pt3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>आलू कहाँ उगते हैं?</t>
+          <t>वाह! अब आपकी बारी।</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>vo_o_opt_ped</t>
+          <t>vo_review_puzzle_cards</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>पेड़ पर</t>
+          <t>प्रश्नचिह्न पर टैप करके प्रश्नों के उत्तर दीजिए। फिर चित्र के टुकड़ों को खिसकाकर चित्र पूरा कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>vo_o_opt_mitti</t>
+          <t>vo_q_soil</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>मिट्टी के अंदर</t>
+          <t>आलू कहाँ उगते हैं?</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>vo_review_water_option</t>
+          <t>vo_o_opt_ped</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>पानी के अंदर।</t>
+          <t>पेड़ पर</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>vo_review_soil_hint3</t>
+          <t>vo_o_opt_mitti</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>आलू मिट्टी के अंदर उगते हैं। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>मिट्टी के अंदर</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>vo_q_sad</t>
+          <t>vo_review_water_option</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>आलू न मिलने पर मालू कैसा महसूस कर रहा था?</t>
+          <t>पानी के अंदर।</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>vo_o_face_udaas</t>
+          <t>vo_review_soil_hint3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>उदास</t>
+          <t>आलू मिट्टी के अंदर उगते हैं। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>vo_o_face_dara</t>
+          <t>vo_q_sad</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>डरा हुआ</t>
+          <t>आलू न मिलने पर मालू कैसा महसूस कर रहा था?</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>vo_o_face_khush</t>
+          <t>vo_o_face_udaas</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>खुश</t>
+          <t>उदास</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>vo_review_sad_hint3</t>
+          <t>vo_o_face_dara</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>मालू उदास हो गया था। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>डरा हुआ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>vo_q_basket</t>
+          <t>vo_o_face_khush</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>मालू ने दादी के आगे खाली टोकरी क्यों रख दी थी?</t>
+          <t>खुश</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>vo_o_t_bhookh</t>
+          <t>vo_review_sad_hint3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>उसे भूख लगी थी</t>
+          <t>मालू उदास हो गया था। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>vo_o_t_nahi_mile_v2</t>
+          <t>vo_q_basket</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>उसे आलू नहीं मिले थे</t>
+          <t>मालू ने दादी के आगे खाली टोकरी क्यों रख दी थी?</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>vo_o_t_tooti</t>
+          <t>vo_o_t_bhookh</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>टोकरी टूट गई थी</t>
+          <t>उसे भूख लगी थी</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>vo_review_basket_hint3</t>
+          <t>vo_o_t_nahi_mile_v2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>उसे आलू नहीं मिले थे। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>उसे आलू नहीं मिले थे</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>vo_fill_prompt</t>
+          <t>vo_o_t_tooti</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>सही शब्द चुनकर वाक्य पूरा कीजिए।</t>
+          <t>टोकरी टूट गई थी</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>vo_o_maalu</t>
+          <t>vo_review_basket_hint3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>मालू</t>
+          <t>उसे आलू नहीं मिले थे। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>vo_o_kaalu</t>
+          <t>vo_fill_prompt</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>कालू</t>
+          <t>सही शब्द चुनकर वाक्य पूरा कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>vo_fill_answer</t>
+          <t>vo_o_maalu</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>कालू ने आलू ढूँढ़ने में मालू की मदद की।</t>
+          <t>मालू</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>vo_q_p4</t>
+          <t>vo_o_kaalu</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>दादी ने ‘ध्यान से देखो’ क्यों कहा?</t>
+          <t>कालू</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>vo_o_t_chhipe</t>
+          <t>vo_fill_answer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>आलू मिट्टी में छिपे थे</t>
+          <t>कालू ने आलू ढूँढ़ने में मालू की मदद की।</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>vo_o_t_so_raha</t>
+          <t>vo_q_p4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>मालू सो रहा था</t>
+          <t>दादी ने ‘ध्यान से देखो’ क्यों कहा?</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>vo_o_t_andhera</t>
+          <t>vo_o_t_chhipe</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>बगीचे में अँधेरा था</t>
+          <t>आलू मिट्टी में छिपे थे</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>vo_p4_hint3</t>
+          <t>vo_o_t_so_raha</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>आलू मिट्टी में छिपे थे। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>मालू सो रहा था</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>vo_q_khoj</t>
+          <t>vo_o_t_andhera</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>आलू मिलने पर मालू ने कालू से क्या कहा?</t>
+          <t>बगीचे में अँधेरा था</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>vo_khoj_ghar</t>
+          <t>vo_p4_hint3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>घर चलो, कालू।</t>
+          <t>आलू मिट्टी में छिपे थे। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>vo_khoj_wah</t>
+          <t>vo_q_khoj</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>वाह कालू! ढूँढ़ निकाले आलू।</t>
+          <t>आलू मिलने पर मालू ने कालू से क्या कहा?</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>vo_khoj_khaen</t>
+          <t>vo_khoj_ghar</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>कालू, आओ खाएँ आलू।</t>
+          <t>घर चलो, कालू।</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>vo_khoj_hint3</t>
+          <t>vo_khoj_wah</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>मालू ने कहा, वाह कालू! ढूँढ़ निकाले आलू। यह सही उत्तर है, इसपर टैप कीजिए।</t>
+          <t>वाह कालू! ढूँढ़ निकाले आलू।</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>vo_review_puzzle_assemble</t>
+          <t>vo_khoj_khaen</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>अब चित्र के टुकड़ों को खिसकाकर चित्र पूरा कीजिए।</t>
+          <t>कालू, आओ खाएँ आलू।</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>vo_review_celebrate_v2</t>
+          <t>vo_khoj_hint3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>बहुत बढ़िया, दोस्त! तुमने कमाल कर दिया!</t>
+          <t>मालू ने कहा, वाह कालू! ढूँढ़ निकाले आलू। यह सही उत्तर है, इसपर टैप कीजिए।</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>vo_review_puzzle_assemble</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>अब चित्र के टुकड़ों को खिसकाकर चित्र पूरा कीजिए।</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>vo_review_celebrate_v2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>बहुत बढ़िया, दोस्त! तुमने कमाल कर दिया!</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>sfx_dog_bark</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>SFX (असली रिकॉर्डिंग, AI नहीं): बड़े कुत्ते (St. Bernard) की 3 भारी भौंक — भौं, भौं, भौं (~1.3 सेकंड)। कहानी पेज 8 पर VO “…उसे सुनाई दिया,” के तुरंत बाद बजती है। स्रोत: freesound.org/s/784914 (Primitv094), लाइसेंस CC0।</t>
         </is>
